--- a/research/traditional_assets/database/data/austria/austria_utility_general.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_utility_general.xlsx
@@ -588,94 +588,94 @@
         </is>
       </c>
       <c r="E2">
+        <v>-0.00287</v>
+      </c>
+      <c r="K2">
+        <v>10.1</v>
+      </c>
+      <c r="M2">
+        <v>10.14</v>
+      </c>
+      <c r="N2">
+        <v>0.03484536082474227</v>
+      </c>
+      <c r="O2">
+        <v>1.003960396039604</v>
+      </c>
+      <c r="P2">
+        <v>10.14</v>
+      </c>
+      <c r="Q2">
+        <v>0.03484536082474227</v>
+      </c>
+      <c r="R2">
+        <v>1.003960396039604</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
         <v>0.021</v>
       </c>
-      <c r="K2">
-        <v>12.1</v>
-      </c>
-      <c r="M2">
-        <v>12.15</v>
-      </c>
-      <c r="N2">
-        <v>0.03630116522258739</v>
-      </c>
-      <c r="O2">
-        <v>1.004132231404959</v>
-      </c>
-      <c r="P2">
-        <v>12.15</v>
-      </c>
-      <c r="Q2">
-        <v>0.03630116522258739</v>
-      </c>
-      <c r="R2">
-        <v>1.004132231404959</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0.022</v>
-      </c>
       <c r="V2">
-        <v>6.573050492978786e-05</v>
+        <v>7.216494845360825e-05</v>
       </c>
       <c r="W2">
-        <v>0.1367231638418079</v>
+        <v>0.1080213903743315</v>
       </c>
       <c r="X2">
-        <v>0.03810140292630167</v>
+        <v>0.06843107650857939</v>
       </c>
       <c r="Y2">
-        <v>0.09862176091550623</v>
+        <v>0.03959031386575215</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-0.003406093122140718</v>
+        <v>-0.003609180384051064</v>
       </c>
       <c r="AB2">
-        <v>0.03801869299270298</v>
+        <v>0.06843107650857939</v>
       </c>
       <c r="AC2">
-        <v>-0.0414247861148437</v>
+        <v>-0.07204025689263045</v>
       </c>
       <c r="AD2">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>1.518</v>
+        <v>-0.021</v>
       </c>
       <c r="AH2">
-        <v>0.004580061860575779</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>0.01603498542274052</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>0.004514927814691659</v>
+        <v>-7.217015660923985e-05</v>
       </c>
       <c r="AK2">
-        <v>0.01580953571205399</v>
+        <v>-0.0002655572275825441</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-12.3</v>
+        <v>-10.4</v>
       </c>
       <c r="AQ2">
-        <v>0.0248780487804878</v>
+        <v>0.03240384615384616</v>
       </c>
     </row>
     <row r="3">
@@ -695,94 +695,94 @@
         </is>
       </c>
       <c r="E3">
+        <v>-0.00287</v>
+      </c>
+      <c r="K3">
+        <v>10.1</v>
+      </c>
+      <c r="M3">
+        <v>10.14</v>
+      </c>
+      <c r="N3">
+        <v>0.03484536082474227</v>
+      </c>
+      <c r="O3">
+        <v>1.003960396039604</v>
+      </c>
+      <c r="P3">
+        <v>10.14</v>
+      </c>
+      <c r="Q3">
+        <v>0.03484536082474227</v>
+      </c>
+      <c r="R3">
+        <v>1.003960396039604</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
         <v>0.021</v>
       </c>
-      <c r="K3">
-        <v>12.1</v>
-      </c>
-      <c r="M3">
-        <v>12.15</v>
-      </c>
-      <c r="N3">
-        <v>0.03630116522258739</v>
-      </c>
-      <c r="O3">
-        <v>1.004132231404959</v>
-      </c>
-      <c r="P3">
-        <v>12.15</v>
-      </c>
-      <c r="Q3">
-        <v>0.03630116522258739</v>
-      </c>
-      <c r="R3">
-        <v>1.004132231404959</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0.022</v>
-      </c>
       <c r="V3">
-        <v>6.573050492978786e-05</v>
+        <v>7.216494845360825e-05</v>
       </c>
       <c r="W3">
-        <v>0.1367231638418079</v>
+        <v>0.1080213903743315</v>
       </c>
       <c r="X3">
-        <v>0.03810140292630167</v>
+        <v>0.06843107650857939</v>
       </c>
       <c r="Y3">
-        <v>0.09862176091550623</v>
+        <v>0.03959031386575215</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.003406093122140718</v>
+        <v>-0.003609180384051064</v>
       </c>
       <c r="AB3">
-        <v>0.03801869299270298</v>
+        <v>0.06843107650857939</v>
       </c>
       <c r="AC3">
-        <v>-0.0414247861148437</v>
+        <v>-0.07204025689263045</v>
       </c>
       <c r="AD3">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>1.518</v>
+        <v>-0.021</v>
       </c>
       <c r="AH3">
-        <v>0.004580061860575779</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.01603498542274052</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.004514927814691659</v>
+        <v>-7.217015660923985e-05</v>
       </c>
       <c r="AK3">
-        <v>0.01580953571205399</v>
+        <v>-0.0002655572275825441</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-12.3</v>
+        <v>-10.4</v>
       </c>
       <c r="AQ3">
-        <v>0.0248780487804878</v>
+        <v>0.03240384615384616</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/austria/austria_utility_general.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_utility_general.xlsx
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="E2">
-        <v>-0.00287</v>
+        <v>0.0398</v>
       </c>
       <c r="K2">
-        <v>10.1</v>
+        <v>12</v>
       </c>
       <c r="M2">
-        <v>10.14</v>
+        <v>12.06</v>
       </c>
       <c r="N2">
-        <v>0.03484536082474227</v>
+        <v>0.04723854289071679</v>
       </c>
       <c r="O2">
-        <v>1.003960396039604</v>
+        <v>1.005</v>
       </c>
       <c r="P2">
-        <v>10.14</v>
+        <v>12.06</v>
       </c>
       <c r="Q2">
-        <v>0.03484536082474227</v>
+        <v>0.04723854289071679</v>
       </c>
       <c r="R2">
-        <v>1.003960396039604</v>
+        <v>1.005</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -618,31 +618,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.021</v>
+        <v>0.001</v>
       </c>
       <c r="V2">
-        <v>7.216494845360825e-05</v>
+        <v>3.916960438699569e-06</v>
       </c>
       <c r="W2">
-        <v>0.1080213903743315</v>
+        <v>0.1517067003792668</v>
       </c>
       <c r="X2">
-        <v>0.06843107650857939</v>
+        <v>0.06182912167538672</v>
       </c>
       <c r="Y2">
-        <v>0.03959031386575215</v>
+        <v>0.08987757870388004</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-0.003609180384051064</v>
+        <v>-0.004173042147725693</v>
       </c>
       <c r="AB2">
-        <v>0.06843107650857939</v>
+        <v>0.06182912167538672</v>
       </c>
       <c r="AC2">
-        <v>-0.07204025689263045</v>
+        <v>-0.06600216382311241</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -654,7 +654,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-0.021</v>
+        <v>-0.001</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -663,19 +663,22 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-7.217015660923985e-05</v>
+        <v>-3.916975781338744e-06</v>
       </c>
       <c r="AK2">
-        <v>-0.0002655572275825441</v>
+        <v>-1.156082729280107e-05</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AM2">
-        <v>-10.4</v>
+        <v>-12.399</v>
+      </c>
+      <c r="AO2">
+        <v>-330</v>
       </c>
       <c r="AQ2">
-        <v>0.03240384615384616</v>
+        <v>0.02661504960077425</v>
       </c>
     </row>
     <row r="3">
@@ -695,28 +698,28 @@
         </is>
       </c>
       <c r="E3">
-        <v>-0.00287</v>
+        <v>0.0398</v>
       </c>
       <c r="K3">
-        <v>10.1</v>
+        <v>12</v>
       </c>
       <c r="M3">
-        <v>10.14</v>
+        <v>12.06</v>
       </c>
       <c r="N3">
-        <v>0.03484536082474227</v>
+        <v>0.04723854289071679</v>
       </c>
       <c r="O3">
-        <v>1.003960396039604</v>
+        <v>1.005</v>
       </c>
       <c r="P3">
-        <v>10.14</v>
+        <v>12.06</v>
       </c>
       <c r="Q3">
-        <v>0.03484536082474227</v>
+        <v>0.04723854289071679</v>
       </c>
       <c r="R3">
-        <v>1.003960396039604</v>
+        <v>1.005</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -725,31 +728,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.021</v>
+        <v>0.001</v>
       </c>
       <c r="V3">
-        <v>7.216494845360825e-05</v>
+        <v>3.916960438699569e-06</v>
       </c>
       <c r="W3">
-        <v>0.1080213903743315</v>
+        <v>0.1517067003792668</v>
       </c>
       <c r="X3">
-        <v>0.06843107650857939</v>
+        <v>0.06182912167538672</v>
       </c>
       <c r="Y3">
-        <v>0.03959031386575215</v>
+        <v>0.08987757870388004</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.003609180384051064</v>
+        <v>-0.004173042147725693</v>
       </c>
       <c r="AB3">
-        <v>0.06843107650857939</v>
+        <v>0.06182912167538672</v>
       </c>
       <c r="AC3">
-        <v>-0.07204025689263045</v>
+        <v>-0.06600216382311241</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -761,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.021</v>
+        <v>-0.001</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -770,19 +773,22 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-7.217015660923985e-05</v>
+        <v>-3.916975781338744e-06</v>
       </c>
       <c r="AK3">
-        <v>-0.0002655572275825441</v>
+        <v>-1.156082729280107e-05</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AM3">
-        <v>-10.4</v>
+        <v>-12.399</v>
+      </c>
+      <c r="AO3">
+        <v>-330</v>
       </c>
       <c r="AQ3">
-        <v>0.03240384615384616</v>
+        <v>0.02661504960077425</v>
       </c>
     </row>
   </sheetData>
